--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132844246</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,616 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133643458</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyren, Långmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475964</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6572330</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133643196</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476080</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572316</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133643476</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyren, Långmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475964</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6572332</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133643026</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Balsammyren, Balsammyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476231</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572226</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133648603</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476052</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6572348</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133643026</v>
+        <v>133648603</v>
       </c>
       <c r="B6" t="n">
-        <v>58332</v>
+        <v>57145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balsammyren, Balsammyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476231</v>
+        <v>476052</v>
       </c>
       <c r="R6" t="n">
-        <v>6572226</v>
+        <v>6572348</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133648603</v>
+        <v>133643026</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>58332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,42 +1305,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Balsammyren, Balsammyren, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476052</v>
+        <v>476231</v>
       </c>
       <c r="R7" t="n">
-        <v>6572348</v>
+        <v>6572226</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,6 +1409,138 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133672607</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Balsammyren, Balsammyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476311</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6572300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hack i stubbe</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133648603</v>
+        <v>133643026</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>58332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Balsammyren, Balsammyren, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476052</v>
+        <v>476231</v>
       </c>
       <c r="R6" t="n">
-        <v>6572348</v>
+        <v>6572226</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133643026</v>
+        <v>133648603</v>
       </c>
       <c r="B7" t="n">
-        <v>58332</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,42 +1305,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Balsammyren, Balsammyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476231</v>
+        <v>476052</v>
       </c>
       <c r="R7" t="n">
-        <v>6572226</v>
+        <v>6572348</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>133643458</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>133643196</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>133643476</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133643026</v>
+        <v>133648603</v>
       </c>
       <c r="B6" t="n">
-        <v>58332</v>
+        <v>57152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balsammyren, Balsammyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476231</v>
+        <v>476052</v>
       </c>
       <c r="R6" t="n">
-        <v>6572226</v>
+        <v>6572348</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133648603</v>
+        <v>133643026</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>58339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,42 +1305,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Balsammyren, Balsammyren, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476052</v>
+        <v>476231</v>
       </c>
       <c r="R7" t="n">
-        <v>6572348</v>
+        <v>6572226</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
         <v>133672607</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>133643458</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>133643196</v>
       </c>
       <c r="B4" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>133643476</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>133648603</v>
       </c>
       <c r="B6" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>133643026</v>
       </c>
       <c r="B7" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>133672607</v>
       </c>
       <c r="B8" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133648603</v>
+        <v>133643026</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Balsammyren, Balsammyren, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476052</v>
+        <v>476231</v>
       </c>
       <c r="R6" t="n">
-        <v>6572348</v>
+        <v>6572226</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133643026</v>
+        <v>133648603</v>
       </c>
       <c r="B7" t="n">
-        <v>58349</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,42 +1305,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Balsammyren, Balsammyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476231</v>
+        <v>476052</v>
       </c>
       <c r="R7" t="n">
-        <v>6572226</v>
+        <v>6572348</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133643026</v>
+        <v>133648603</v>
       </c>
       <c r="B6" t="n">
-        <v>58349</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,42 +1188,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balsammyren, Balsammyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476231</v>
+        <v>476052</v>
       </c>
       <c r="R6" t="n">
-        <v>6572226</v>
+        <v>6572348</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133648603</v>
+        <v>133643026</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,42 +1305,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Balsammyren, Balsammyren, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476052</v>
+        <v>476231</v>
       </c>
       <c r="R7" t="n">
-        <v>6572348</v>
+        <v>6572226</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132844246</v>
+        <v>133643458</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,56 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476047</v>
+        <v>475964</v>
       </c>
       <c r="R2" t="n">
-        <v>6572354</v>
+        <v>6572330</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,30 +776,55 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133643458</v>
+        <v>133643476</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,7 +848,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +860,10 @@
         <v>475964</v>
       </c>
       <c r="R3" t="n">
-        <v>6572330</v>
+        <v>6572332</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:34</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall.</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,26 +917,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133643196</v>
+        <v>133672607</v>
       </c>
       <c r="B4" t="n">
-        <v>58658</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,16 +945,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -974,22 +965,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
+          <t>Balsammyren, Balsammyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476080</v>
+        <v>476311</v>
       </c>
       <c r="R4" t="n">
-        <v>6572316</v>
+        <v>6572300</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,22 +1004,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>05:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack i stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +1039,16 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,53 +1066,67 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133643476</v>
+        <v>132844246</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475964</v>
+        <v>476047</v>
       </c>
       <c r="R5" t="n">
-        <v>6572332</v>
+        <v>6572354</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,22 +1150,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,21 +1176,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1411,27 +1426,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133672607</v>
+        <v>133643196</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1442,22 +1457,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Balsammyren, Balsammyren, Vrm</t>
+          <t>Västra Stockholmsåsen, Västra Stockholmsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476311</v>
+        <v>476080</v>
       </c>
       <c r="R8" t="n">
-        <v>6572300</v>
+        <v>6572316</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,27 +1496,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:19</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hack i stubbe</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,16 +1526,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stump</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 20111-2026 artfynd.xlsx
+++ b/artfynd/A 20111-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133643458</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133643476</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1063,6 +1078,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133672607</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1189,6 +1209,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844246</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1306,6 +1331,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133648603</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1423,6 +1453,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133643026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,8 +1575,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133643196</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>